--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -399,7 +399,7 @@
     <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
-    <t>Synonyme FINESS : date de mise en œuvre</t>
+    <t>Synonyme : date de mise en œuvre, datePremiereMEO</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -424,7 +424,7 @@
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
-    <t>Synonyme FINESS : date de fin de mise en œuvre</t>
+    <t>Synonyme : date de fin de mise en œuvre, dateFin</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
